--- a/AAII_Financials/Yearly/MYTE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MYTE_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -718,22 +718,22 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>834000</v>
+        <v>836300</v>
       </c>
       <c r="E8" s="3">
-        <v>748400</v>
+        <v>750500</v>
       </c>
       <c r="F8" s="3">
-        <v>664100</v>
+        <v>666000</v>
       </c>
       <c r="G8" s="3">
-        <v>487700</v>
+        <v>489100</v>
       </c>
       <c r="H8" s="3">
-        <v>411300</v>
+        <v>412500</v>
       </c>
       <c r="I8" s="3">
-        <v>329300</v>
+        <v>330300</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
@@ -754,22 +754,22 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>418800</v>
+        <v>420000</v>
       </c>
       <c r="E9" s="3">
-        <v>363200</v>
+        <v>364300</v>
       </c>
       <c r="F9" s="3">
-        <v>352700</v>
+        <v>353700</v>
       </c>
       <c r="G9" s="3">
-        <v>259900</v>
+        <v>260700</v>
       </c>
       <c r="H9" s="3">
-        <v>218500</v>
+        <v>219200</v>
       </c>
       <c r="I9" s="3">
-        <v>174100</v>
+        <v>174600</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -790,22 +790,22 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>415100</v>
+        <v>416300</v>
       </c>
       <c r="E10" s="3">
-        <v>385200</v>
+        <v>386300</v>
       </c>
       <c r="F10" s="3">
-        <v>311400</v>
+        <v>312300</v>
       </c>
       <c r="G10" s="3">
-        <v>227800</v>
+        <v>228400</v>
       </c>
       <c r="H10" s="3">
-        <v>192800</v>
+        <v>193300</v>
       </c>
       <c r="I10" s="3">
-        <v>155200</v>
+        <v>155700</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -950,19 +950,19 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>12600</v>
+        <v>12700</v>
       </c>
       <c r="E15" s="3">
         <v>9900</v>
       </c>
       <c r="F15" s="3">
-        <v>8900</v>
+        <v>9000</v>
       </c>
       <c r="G15" s="3">
         <v>8600</v>
       </c>
       <c r="H15" s="3">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="I15" s="3">
         <v>7400</v>
@@ -999,22 +999,22 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>840500</v>
+        <v>842900</v>
       </c>
       <c r="E17" s="3">
-        <v>743100</v>
+        <v>745300</v>
       </c>
       <c r="F17" s="3">
-        <v>699000</v>
+        <v>701000</v>
       </c>
       <c r="G17" s="3">
-        <v>465000</v>
+        <v>466300</v>
       </c>
       <c r="H17" s="3">
-        <v>390600</v>
+        <v>391700</v>
       </c>
       <c r="I17" s="3">
-        <v>314300</v>
+        <v>315200</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
@@ -1038,16 +1038,16 @@
         <v>-6600</v>
       </c>
       <c r="E18" s="3">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="F18" s="3">
-        <v>-34900</v>
+        <v>-35000</v>
       </c>
       <c r="G18" s="3">
-        <v>22700</v>
+        <v>22800</v>
       </c>
       <c r="H18" s="3">
-        <v>20700</v>
+        <v>20800</v>
       </c>
       <c r="I18" s="3">
         <v>15000</v>
@@ -1093,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>24300</v>
+        <v>24400</v>
       </c>
       <c r="G20" s="3">
         <v>-2300</v>
@@ -1102,7 +1102,7 @@
         <v>-5100</v>
       </c>
       <c r="I20" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1123,22 +1123,22 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="E21" s="3">
-        <v>15100</v>
+        <v>15200</v>
       </c>
       <c r="F21" s="3">
         <v>-1600</v>
       </c>
       <c r="G21" s="3">
-        <v>28900</v>
+        <v>29000</v>
       </c>
       <c r="H21" s="3">
-        <v>24000</v>
+        <v>24100</v>
       </c>
       <c r="I21" s="3">
-        <v>26500</v>
+        <v>26600</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
@@ -1165,10 +1165,10 @@
         <v>1100</v>
       </c>
       <c r="F22" s="3">
-        <v>7900</v>
+        <v>8000</v>
       </c>
       <c r="G22" s="3">
-        <v>9700</v>
+        <v>9800</v>
       </c>
       <c r="H22" s="3">
         <v>10100</v>
@@ -1195,22 +1195,22 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-9200</v>
+        <v>-9300</v>
       </c>
       <c r="E23" s="3">
         <v>4200</v>
       </c>
       <c r="F23" s="3">
-        <v>-18500</v>
+        <v>-18600</v>
       </c>
       <c r="G23" s="3">
-        <v>10600</v>
+        <v>10700</v>
       </c>
       <c r="H23" s="3">
         <v>5500</v>
       </c>
       <c r="I23" s="3">
-        <v>9700</v>
+        <v>9800</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
@@ -1234,7 +1234,7 @@
         <v>7200</v>
       </c>
       <c r="E24" s="3">
-        <v>12700</v>
+        <v>12800</v>
       </c>
       <c r="F24" s="3">
         <v>16900</v>
@@ -1303,13 +1303,13 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-16400</v>
+        <v>-16500</v>
       </c>
       <c r="E26" s="3">
         <v>-8600</v>
       </c>
       <c r="F26" s="3">
-        <v>-35400</v>
+        <v>-35500</v>
       </c>
       <c r="G26" s="3">
         <v>6900</v>
@@ -1339,13 +1339,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-16400</v>
+        <v>-16500</v>
       </c>
       <c r="E27" s="3">
         <v>-8600</v>
       </c>
       <c r="F27" s="3">
-        <v>-35400</v>
+        <v>-35500</v>
       </c>
       <c r="G27" s="3">
         <v>6900</v>
@@ -1525,7 +1525,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-24300</v>
+        <v>-24400</v>
       </c>
       <c r="G32" s="3">
         <v>2300</v>
@@ -1534,7 +1534,7 @@
         <v>5100</v>
       </c>
       <c r="I32" s="3">
-        <v>-4100</v>
+        <v>-4200</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1555,13 +1555,13 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-16400</v>
+        <v>-16500</v>
       </c>
       <c r="E33" s="3">
         <v>-8600</v>
       </c>
       <c r="F33" s="3">
-        <v>-35400</v>
+        <v>-35500</v>
       </c>
       <c r="G33" s="3">
         <v>6900</v>
@@ -1627,13 +1627,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-16400</v>
+        <v>-16500</v>
       </c>
       <c r="E35" s="3">
         <v>-8600</v>
       </c>
       <c r="F35" s="3">
-        <v>-35400</v>
+        <v>-35500</v>
       </c>
       <c r="G35" s="3">
         <v>6900</v>
@@ -1736,13 +1736,13 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>32700</v>
+        <v>32800</v>
       </c>
       <c r="E41" s="3">
-        <v>123200</v>
+        <v>123500</v>
       </c>
       <c r="F41" s="3">
-        <v>83300</v>
+        <v>83500</v>
       </c>
       <c r="G41" s="3">
         <v>10200</v>
@@ -1844,22 +1844,22 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>390900</v>
+        <v>392000</v>
       </c>
       <c r="E44" s="3">
-        <v>249700</v>
+        <v>250400</v>
       </c>
       <c r="F44" s="3">
-        <v>268100</v>
+        <v>268800</v>
       </c>
       <c r="G44" s="3">
-        <v>183500</v>
+        <v>184000</v>
       </c>
       <c r="H44" s="3">
-        <v>147600</v>
+        <v>148000</v>
       </c>
       <c r="I44" s="3">
-        <v>115800</v>
+        <v>116100</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
@@ -1880,13 +1880,13 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>45700</v>
+        <v>45800</v>
       </c>
       <c r="E45" s="3">
-        <v>67100</v>
+        <v>67300</v>
       </c>
       <c r="F45" s="3">
-        <v>15900</v>
+        <v>16000</v>
       </c>
       <c r="G45" s="3">
         <v>20600</v>
@@ -1895,7 +1895,7 @@
         <v>9200</v>
       </c>
       <c r="I45" s="3">
-        <v>9800</v>
+        <v>9900</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -1916,22 +1916,22 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>477400</v>
+        <v>478800</v>
       </c>
       <c r="E46" s="3">
-        <v>449000</v>
+        <v>450300</v>
       </c>
       <c r="F46" s="3">
-        <v>372700</v>
+        <v>373800</v>
       </c>
       <c r="G46" s="3">
-        <v>219500</v>
+        <v>220100</v>
       </c>
       <c r="H46" s="3">
-        <v>165200</v>
+        <v>165700</v>
       </c>
       <c r="I46" s="3">
-        <v>135700</v>
+        <v>136000</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
@@ -1952,7 +1952,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>7100</v>
+        <v>7200</v>
       </c>
       <c r="E47" s="3">
         <v>300</v>
@@ -1988,22 +1988,22 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>99800</v>
+        <v>100100</v>
       </c>
       <c r="E48" s="3">
-        <v>42700</v>
+        <v>42800</v>
       </c>
       <c r="F48" s="3">
         <v>24800</v>
       </c>
       <c r="G48" s="3">
-        <v>31000</v>
+        <v>31100</v>
       </c>
       <c r="H48" s="3">
         <v>29900</v>
       </c>
       <c r="I48" s="3">
-        <v>36200</v>
+        <v>36300</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
@@ -2024,22 +2024,22 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>168500</v>
+        <v>169000</v>
       </c>
       <c r="E49" s="3">
-        <v>168400</v>
+        <v>168900</v>
       </c>
       <c r="F49" s="3">
-        <v>168800</v>
+        <v>169300</v>
       </c>
       <c r="G49" s="3">
-        <v>168100</v>
+        <v>168600</v>
       </c>
       <c r="H49" s="3">
-        <v>168400</v>
+        <v>168900</v>
       </c>
       <c r="I49" s="3">
-        <v>168200</v>
+        <v>168700</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
@@ -2204,22 +2204,22 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>753000</v>
+        <v>755100</v>
       </c>
       <c r="E54" s="3">
-        <v>667000</v>
+        <v>668900</v>
       </c>
       <c r="F54" s="3">
-        <v>566300</v>
+        <v>567900</v>
       </c>
       <c r="G54" s="3">
-        <v>418600</v>
+        <v>419800</v>
       </c>
       <c r="H54" s="3">
-        <v>363600</v>
+        <v>364700</v>
       </c>
       <c r="I54" s="3">
-        <v>340200</v>
+        <v>341200</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
@@ -2272,22 +2272,22 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>77100</v>
+        <v>77300</v>
       </c>
       <c r="E57" s="3">
-        <v>49000</v>
+        <v>49100</v>
       </c>
       <c r="F57" s="3">
-        <v>47300</v>
+        <v>47400</v>
       </c>
       <c r="G57" s="3">
-        <v>39200</v>
+        <v>39300</v>
       </c>
       <c r="H57" s="3">
-        <v>31900</v>
+        <v>32000</v>
       </c>
       <c r="I57" s="3">
-        <v>33900</v>
+        <v>34000</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
@@ -2308,7 +2308,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>8800</v>
+        <v>8900</v>
       </c>
       <c r="E58" s="3">
         <v>5600</v>
@@ -2317,10 +2317,10 @@
         <v>5800</v>
       </c>
       <c r="G58" s="3">
-        <v>17100</v>
+        <v>17200</v>
       </c>
       <c r="H58" s="3">
-        <v>9000</v>
+        <v>9100</v>
       </c>
       <c r="I58" s="3">
         <v>5400</v>
@@ -2344,22 +2344,22 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>124100</v>
+        <v>124500</v>
       </c>
       <c r="E59" s="3">
-        <v>121000</v>
+        <v>121400</v>
       </c>
       <c r="F59" s="3">
-        <v>81900</v>
+        <v>82100</v>
       </c>
       <c r="G59" s="3">
-        <v>57400</v>
+        <v>57500</v>
       </c>
       <c r="H59" s="3">
-        <v>38900</v>
+        <v>39000</v>
       </c>
       <c r="I59" s="3">
-        <v>26800</v>
+        <v>26900</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
@@ -2380,22 +2380,22 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>210100</v>
+        <v>210700</v>
       </c>
       <c r="E60" s="3">
-        <v>175600</v>
+        <v>176100</v>
       </c>
       <c r="F60" s="3">
-        <v>135000</v>
+        <v>135400</v>
       </c>
       <c r="G60" s="3">
-        <v>113700</v>
+        <v>114100</v>
       </c>
       <c r="H60" s="3">
-        <v>79900</v>
+        <v>80100</v>
       </c>
       <c r="I60" s="3">
-        <v>66200</v>
+        <v>66400</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
@@ -2416,22 +2416,22 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>53700</v>
+        <v>53900</v>
       </c>
       <c r="E61" s="3">
-        <v>18200</v>
+        <v>18300</v>
       </c>
       <c r="F61" s="3">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="G61" s="3">
-        <v>222600</v>
+        <v>223200</v>
       </c>
       <c r="H61" s="3">
-        <v>151600</v>
+        <v>152100</v>
       </c>
       <c r="I61" s="3">
-        <v>143800</v>
+        <v>144200</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>3300</v>
       </c>
       <c r="G62" s="3">
-        <v>12400</v>
+        <v>12500</v>
       </c>
       <c r="H62" s="3">
         <v>11400</v>
@@ -2596,22 +2596,22 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>267500</v>
+        <v>268300</v>
       </c>
       <c r="E66" s="3">
-        <v>198700</v>
+        <v>199200</v>
       </c>
       <c r="F66" s="3">
-        <v>147800</v>
+        <v>148200</v>
       </c>
       <c r="G66" s="3">
-        <v>348700</v>
+        <v>349700</v>
       </c>
       <c r="H66" s="3">
-        <v>242900</v>
+        <v>243500</v>
       </c>
       <c r="I66" s="3">
-        <v>222900</v>
+        <v>223500</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
@@ -2792,22 +2792,22 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>483800</v>
+        <v>485200</v>
       </c>
       <c r="E72" s="3">
-        <v>466700</v>
+        <v>468000</v>
       </c>
       <c r="F72" s="3">
-        <v>416800</v>
+        <v>418000</v>
       </c>
       <c r="G72" s="3">
-        <v>68100</v>
+        <v>68300</v>
       </c>
       <c r="H72" s="3">
-        <v>124100</v>
+        <v>124500</v>
       </c>
       <c r="I72" s="3">
-        <v>122100</v>
+        <v>122500</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
@@ -2936,22 +2936,22 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>485500</v>
+        <v>486800</v>
       </c>
       <c r="E76" s="3">
-        <v>468400</v>
+        <v>469700</v>
       </c>
       <c r="F76" s="3">
-        <v>418500</v>
+        <v>419700</v>
       </c>
       <c r="G76" s="3">
-        <v>69800</v>
+        <v>70000</v>
       </c>
       <c r="H76" s="3">
-        <v>120800</v>
+        <v>121100</v>
       </c>
       <c r="I76" s="3">
-        <v>117300</v>
+        <v>117600</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
@@ -3049,13 +3049,13 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-16400</v>
+        <v>-16500</v>
       </c>
       <c r="E81" s="3">
         <v>-8600</v>
       </c>
       <c r="F81" s="3">
-        <v>-35400</v>
+        <v>-35500</v>
       </c>
       <c r="G81" s="3">
         <v>6900</v>
@@ -3101,19 +3101,19 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>12600</v>
+        <v>12700</v>
       </c>
       <c r="E83" s="3">
         <v>9900</v>
       </c>
       <c r="F83" s="3">
-        <v>8900</v>
+        <v>9000</v>
       </c>
       <c r="G83" s="3">
         <v>8600</v>
       </c>
       <c r="H83" s="3">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="I83" s="3">
         <v>7400</v>
@@ -3317,13 +3317,13 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-59700</v>
+        <v>-59900</v>
       </c>
       <c r="E89" s="3">
-        <v>59500</v>
+        <v>59600</v>
       </c>
       <c r="F89" s="3">
-        <v>-18000</v>
+        <v>-18100</v>
       </c>
       <c r="G89" s="3">
         <v>11500</v>
@@ -3369,10 +3369,10 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-24700</v>
+        <v>-24800</v>
       </c>
       <c r="E91" s="3">
-        <v>-12900</v>
+        <v>-13000</v>
       </c>
       <c r="F91" s="3">
         <v>-3200</v>
@@ -3477,10 +3477,10 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-24700</v>
+        <v>-24800</v>
       </c>
       <c r="E94" s="3">
-        <v>-12900</v>
+        <v>-13000</v>
       </c>
       <c r="F94" s="3">
         <v>-3100</v>
@@ -3679,7 +3679,7 @@
         <v>-6600</v>
       </c>
       <c r="F100" s="3">
-        <v>94300</v>
+        <v>94600</v>
       </c>
       <c r="G100" s="3">
         <v>-1000</v>
@@ -3745,13 +3745,13 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-90500</v>
+        <v>-90700</v>
       </c>
       <c r="E102" s="3">
-        <v>39900</v>
+        <v>40000</v>
       </c>
       <c r="F102" s="3">
-        <v>73100</v>
+        <v>73300</v>
       </c>
       <c r="G102" s="3">
         <v>7900</v>

--- a/AAII_Financials/Yearly/MYTE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MYTE_YR_FIN.xlsx
@@ -718,22 +718,22 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>836300</v>
+        <v>830600</v>
       </c>
       <c r="E8" s="3">
-        <v>750500</v>
+        <v>745400</v>
       </c>
       <c r="F8" s="3">
-        <v>666000</v>
+        <v>661500</v>
       </c>
       <c r="G8" s="3">
-        <v>489100</v>
+        <v>485800</v>
       </c>
       <c r="H8" s="3">
-        <v>412500</v>
+        <v>409700</v>
       </c>
       <c r="I8" s="3">
-        <v>330300</v>
+        <v>328000</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
@@ -754,22 +754,22 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>420000</v>
+        <v>417200</v>
       </c>
       <c r="E9" s="3">
-        <v>364300</v>
+        <v>361800</v>
       </c>
       <c r="F9" s="3">
-        <v>353700</v>
+        <v>351300</v>
       </c>
       <c r="G9" s="3">
-        <v>260700</v>
+        <v>258900</v>
       </c>
       <c r="H9" s="3">
-        <v>219200</v>
+        <v>217700</v>
       </c>
       <c r="I9" s="3">
-        <v>174600</v>
+        <v>173400</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -790,22 +790,22 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>416300</v>
+        <v>413500</v>
       </c>
       <c r="E10" s="3">
-        <v>386300</v>
+        <v>383600</v>
       </c>
       <c r="F10" s="3">
-        <v>312300</v>
+        <v>310200</v>
       </c>
       <c r="G10" s="3">
-        <v>228400</v>
+        <v>226900</v>
       </c>
       <c r="H10" s="3">
-        <v>193300</v>
+        <v>192000</v>
       </c>
       <c r="I10" s="3">
-        <v>155700</v>
+        <v>154600</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -920,7 +920,7 @@
         <v>4700</v>
       </c>
       <c r="F14" s="3">
-        <v>7600</v>
+        <v>7500</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -950,22 +950,22 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>12700</v>
+        <v>12600</v>
       </c>
       <c r="E15" s="3">
-        <v>9900</v>
+        <v>9800</v>
       </c>
       <c r="F15" s="3">
-        <v>9000</v>
+        <v>8900</v>
       </c>
       <c r="G15" s="3">
-        <v>8600</v>
+        <v>8500</v>
       </c>
       <c r="H15" s="3">
-        <v>8400</v>
+        <v>8300</v>
       </c>
       <c r="I15" s="3">
-        <v>7400</v>
+        <v>7300</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>3</v>
@@ -999,22 +999,22 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>842900</v>
+        <v>837200</v>
       </c>
       <c r="E17" s="3">
-        <v>745300</v>
+        <v>740200</v>
       </c>
       <c r="F17" s="3">
-        <v>701000</v>
+        <v>696200</v>
       </c>
       <c r="G17" s="3">
-        <v>466300</v>
+        <v>463200</v>
       </c>
       <c r="H17" s="3">
-        <v>391700</v>
+        <v>389100</v>
       </c>
       <c r="I17" s="3">
-        <v>315200</v>
+        <v>313100</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
@@ -1038,19 +1038,19 @@
         <v>-6600</v>
       </c>
       <c r="E18" s="3">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="F18" s="3">
-        <v>-35000</v>
+        <v>-34800</v>
       </c>
       <c r="G18" s="3">
-        <v>22800</v>
+        <v>22600</v>
       </c>
       <c r="H18" s="3">
-        <v>20800</v>
+        <v>20600</v>
       </c>
       <c r="I18" s="3">
-        <v>15000</v>
+        <v>14900</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
@@ -1093,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>24400</v>
+        <v>24200</v>
       </c>
       <c r="G20" s="3">
         <v>-2300</v>
@@ -1102,7 +1102,7 @@
         <v>-5100</v>
       </c>
       <c r="I20" s="3">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1123,22 +1123,22 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>6500</v>
+        <v>6300</v>
       </c>
       <c r="E21" s="3">
-        <v>15200</v>
+        <v>15000</v>
       </c>
       <c r="F21" s="3">
-        <v>-1600</v>
+        <v>-1700</v>
       </c>
       <c r="G21" s="3">
-        <v>29000</v>
+        <v>28700</v>
       </c>
       <c r="H21" s="3">
-        <v>24100</v>
+        <v>23800</v>
       </c>
       <c r="I21" s="3">
-        <v>26600</v>
+        <v>26300</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
@@ -1159,16 +1159,16 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="E22" s="3">
         <v>1100</v>
       </c>
       <c r="F22" s="3">
-        <v>8000</v>
+        <v>7900</v>
       </c>
       <c r="G22" s="3">
-        <v>9800</v>
+        <v>9700</v>
       </c>
       <c r="H22" s="3">
         <v>10100</v>
@@ -1195,22 +1195,22 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-9300</v>
+        <v>-9200</v>
       </c>
       <c r="E23" s="3">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="F23" s="3">
-        <v>-18600</v>
+        <v>-18400</v>
       </c>
       <c r="G23" s="3">
-        <v>10700</v>
+        <v>10600</v>
       </c>
       <c r="H23" s="3">
         <v>5500</v>
       </c>
       <c r="I23" s="3">
-        <v>9800</v>
+        <v>9700</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
@@ -1231,13 +1231,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>7200</v>
+        <v>7100</v>
       </c>
       <c r="E24" s="3">
-        <v>12800</v>
+        <v>12700</v>
       </c>
       <c r="F24" s="3">
-        <v>16900</v>
+        <v>16800</v>
       </c>
       <c r="G24" s="3">
         <v>3700</v>
@@ -1246,7 +1246,7 @@
         <v>3700</v>
       </c>
       <c r="I24" s="3">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
@@ -1303,13 +1303,13 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-16500</v>
+        <v>-16300</v>
       </c>
       <c r="E26" s="3">
-        <v>-8600</v>
+        <v>-8500</v>
       </c>
       <c r="F26" s="3">
-        <v>-35500</v>
+        <v>-35200</v>
       </c>
       <c r="G26" s="3">
         <v>6900</v>
@@ -1318,7 +1318,7 @@
         <v>1800</v>
       </c>
       <c r="I26" s="3">
-        <v>6000</v>
+        <v>5900</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
@@ -1339,13 +1339,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-16500</v>
+        <v>-16300</v>
       </c>
       <c r="E27" s="3">
-        <v>-8600</v>
+        <v>-8500</v>
       </c>
       <c r="F27" s="3">
-        <v>-35500</v>
+        <v>-35200</v>
       </c>
       <c r="G27" s="3">
         <v>6900</v>
@@ -1354,7 +1354,7 @@
         <v>1800</v>
       </c>
       <c r="I27" s="3">
-        <v>6000</v>
+        <v>5900</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
@@ -1525,7 +1525,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-24400</v>
+        <v>-24200</v>
       </c>
       <c r="G32" s="3">
         <v>2300</v>
@@ -1534,7 +1534,7 @@
         <v>5100</v>
       </c>
       <c r="I32" s="3">
-        <v>-4200</v>
+        <v>-4100</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1555,13 +1555,13 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-16500</v>
+        <v>-16300</v>
       </c>
       <c r="E33" s="3">
-        <v>-8600</v>
+        <v>-8500</v>
       </c>
       <c r="F33" s="3">
-        <v>-35500</v>
+        <v>-35200</v>
       </c>
       <c r="G33" s="3">
         <v>6900</v>
@@ -1570,7 +1570,7 @@
         <v>1800</v>
       </c>
       <c r="I33" s="3">
-        <v>6000</v>
+        <v>5900</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
@@ -1627,13 +1627,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-16500</v>
+        <v>-16300</v>
       </c>
       <c r="E35" s="3">
-        <v>-8600</v>
+        <v>-8500</v>
       </c>
       <c r="F35" s="3">
-        <v>-35500</v>
+        <v>-35200</v>
       </c>
       <c r="G35" s="3">
         <v>6900</v>
@@ -1642,7 +1642,7 @@
         <v>1800</v>
       </c>
       <c r="I35" s="3">
-        <v>6000</v>
+        <v>5900</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
@@ -1736,16 +1736,16 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>32800</v>
+        <v>32600</v>
       </c>
       <c r="E41" s="3">
-        <v>123500</v>
+        <v>122700</v>
       </c>
       <c r="F41" s="3">
-        <v>83500</v>
+        <v>83000</v>
       </c>
       <c r="G41" s="3">
-        <v>10200</v>
+        <v>10100</v>
       </c>
       <c r="H41" s="3">
         <v>2300</v>
@@ -1808,13 +1808,13 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>8200</v>
+        <v>8100</v>
       </c>
       <c r="E43" s="3">
-        <v>9000</v>
+        <v>8900</v>
       </c>
       <c r="F43" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="G43" s="3">
         <v>5200</v>
@@ -1844,22 +1844,22 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>392000</v>
+        <v>389300</v>
       </c>
       <c r="E44" s="3">
-        <v>250400</v>
+        <v>248700</v>
       </c>
       <c r="F44" s="3">
-        <v>268800</v>
+        <v>267000</v>
       </c>
       <c r="G44" s="3">
-        <v>184000</v>
+        <v>182800</v>
       </c>
       <c r="H44" s="3">
-        <v>148000</v>
+        <v>147000</v>
       </c>
       <c r="I44" s="3">
-        <v>116100</v>
+        <v>115300</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
@@ -1880,22 +1880,22 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>45800</v>
+        <v>45500</v>
       </c>
       <c r="E45" s="3">
-        <v>67300</v>
+        <v>66900</v>
       </c>
       <c r="F45" s="3">
-        <v>16000</v>
+        <v>15800</v>
       </c>
       <c r="G45" s="3">
-        <v>20600</v>
+        <v>20500</v>
       </c>
       <c r="H45" s="3">
-        <v>9200</v>
+        <v>9100</v>
       </c>
       <c r="I45" s="3">
-        <v>9900</v>
+        <v>9800</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -1916,22 +1916,22 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>478800</v>
+        <v>475500</v>
       </c>
       <c r="E46" s="3">
-        <v>450300</v>
+        <v>447200</v>
       </c>
       <c r="F46" s="3">
-        <v>373800</v>
+        <v>371200</v>
       </c>
       <c r="G46" s="3">
-        <v>220100</v>
+        <v>218600</v>
       </c>
       <c r="H46" s="3">
-        <v>165700</v>
+        <v>164500</v>
       </c>
       <c r="I46" s="3">
-        <v>136000</v>
+        <v>135100</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
@@ -1952,7 +1952,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>7200</v>
+        <v>7100</v>
       </c>
       <c r="E47" s="3">
         <v>300</v>
@@ -1988,22 +1988,22 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>100100</v>
+        <v>99500</v>
       </c>
       <c r="E48" s="3">
-        <v>42800</v>
+        <v>42500</v>
       </c>
       <c r="F48" s="3">
-        <v>24800</v>
+        <v>24700</v>
       </c>
       <c r="G48" s="3">
-        <v>31100</v>
+        <v>30900</v>
       </c>
       <c r="H48" s="3">
-        <v>29900</v>
+        <v>29700</v>
       </c>
       <c r="I48" s="3">
-        <v>36300</v>
+        <v>36100</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
@@ -2024,22 +2024,22 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>169000</v>
+        <v>167800</v>
       </c>
       <c r="E49" s="3">
-        <v>168900</v>
+        <v>167700</v>
       </c>
       <c r="F49" s="3">
-        <v>169300</v>
+        <v>168200</v>
       </c>
       <c r="G49" s="3">
-        <v>168600</v>
+        <v>167500</v>
       </c>
       <c r="H49" s="3">
-        <v>168900</v>
+        <v>167700</v>
       </c>
       <c r="I49" s="3">
-        <v>168700</v>
+        <v>167600</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
@@ -2204,22 +2204,22 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>755100</v>
+        <v>750000</v>
       </c>
       <c r="E54" s="3">
-        <v>668900</v>
+        <v>664400</v>
       </c>
       <c r="F54" s="3">
-        <v>567900</v>
+        <v>564100</v>
       </c>
       <c r="G54" s="3">
-        <v>419800</v>
+        <v>416900</v>
       </c>
       <c r="H54" s="3">
-        <v>364700</v>
+        <v>362200</v>
       </c>
       <c r="I54" s="3">
-        <v>341200</v>
+        <v>338900</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
@@ -2272,22 +2272,22 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>77300</v>
+        <v>76800</v>
       </c>
       <c r="E57" s="3">
-        <v>49100</v>
+        <v>48800</v>
       </c>
       <c r="F57" s="3">
-        <v>47400</v>
+        <v>47100</v>
       </c>
       <c r="G57" s="3">
-        <v>39300</v>
+        <v>39100</v>
       </c>
       <c r="H57" s="3">
-        <v>32000</v>
+        <v>31800</v>
       </c>
       <c r="I57" s="3">
-        <v>34000</v>
+        <v>33800</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
@@ -2308,7 +2308,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>8900</v>
+        <v>8800</v>
       </c>
       <c r="E58" s="3">
         <v>5600</v>
@@ -2317,10 +2317,10 @@
         <v>5800</v>
       </c>
       <c r="G58" s="3">
-        <v>17200</v>
+        <v>17100</v>
       </c>
       <c r="H58" s="3">
-        <v>9100</v>
+        <v>9000</v>
       </c>
       <c r="I58" s="3">
         <v>5400</v>
@@ -2344,22 +2344,22 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>124500</v>
+        <v>123600</v>
       </c>
       <c r="E59" s="3">
-        <v>121400</v>
+        <v>120500</v>
       </c>
       <c r="F59" s="3">
-        <v>82100</v>
+        <v>81600</v>
       </c>
       <c r="G59" s="3">
-        <v>57500</v>
+        <v>57200</v>
       </c>
       <c r="H59" s="3">
-        <v>39000</v>
+        <v>38800</v>
       </c>
       <c r="I59" s="3">
-        <v>26900</v>
+        <v>26700</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
@@ -2380,22 +2380,22 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>210700</v>
+        <v>209300</v>
       </c>
       <c r="E60" s="3">
-        <v>176100</v>
+        <v>174900</v>
       </c>
       <c r="F60" s="3">
-        <v>135400</v>
+        <v>134500</v>
       </c>
       <c r="G60" s="3">
-        <v>114100</v>
+        <v>113300</v>
       </c>
       <c r="H60" s="3">
-        <v>80100</v>
+        <v>79600</v>
       </c>
       <c r="I60" s="3">
-        <v>66400</v>
+        <v>65900</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
@@ -2416,22 +2416,22 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>53900</v>
+        <v>53500</v>
       </c>
       <c r="E61" s="3">
-        <v>18300</v>
+        <v>18200</v>
       </c>
       <c r="F61" s="3">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="G61" s="3">
-        <v>223200</v>
+        <v>221700</v>
       </c>
       <c r="H61" s="3">
-        <v>152100</v>
+        <v>151000</v>
       </c>
       <c r="I61" s="3">
-        <v>144200</v>
+        <v>143200</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="E62" s="3">
         <v>4800</v>
@@ -2461,13 +2461,13 @@
         <v>3300</v>
       </c>
       <c r="G62" s="3">
-        <v>12500</v>
+        <v>12400</v>
       </c>
       <c r="H62" s="3">
-        <v>11400</v>
+        <v>11300</v>
       </c>
       <c r="I62" s="3">
-        <v>12900</v>
+        <v>12800</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -2596,22 +2596,22 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>268300</v>
+        <v>266400</v>
       </c>
       <c r="E66" s="3">
-        <v>199200</v>
+        <v>197900</v>
       </c>
       <c r="F66" s="3">
-        <v>148200</v>
+        <v>147200</v>
       </c>
       <c r="G66" s="3">
-        <v>349700</v>
+        <v>347400</v>
       </c>
       <c r="H66" s="3">
-        <v>243500</v>
+        <v>241900</v>
       </c>
       <c r="I66" s="3">
-        <v>223500</v>
+        <v>222000</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
@@ -2792,22 +2792,22 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>485200</v>
+        <v>481900</v>
       </c>
       <c r="E72" s="3">
-        <v>468000</v>
+        <v>464900</v>
       </c>
       <c r="F72" s="3">
-        <v>418000</v>
+        <v>415100</v>
       </c>
       <c r="G72" s="3">
-        <v>68300</v>
+        <v>67800</v>
       </c>
       <c r="H72" s="3">
-        <v>124500</v>
+        <v>123600</v>
       </c>
       <c r="I72" s="3">
-        <v>122500</v>
+        <v>121700</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
@@ -2936,22 +2936,22 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>486800</v>
+        <v>483500</v>
       </c>
       <c r="E76" s="3">
-        <v>469700</v>
+        <v>466500</v>
       </c>
       <c r="F76" s="3">
-        <v>419700</v>
+        <v>416800</v>
       </c>
       <c r="G76" s="3">
-        <v>70000</v>
+        <v>69600</v>
       </c>
       <c r="H76" s="3">
-        <v>121100</v>
+        <v>120300</v>
       </c>
       <c r="I76" s="3">
-        <v>117600</v>
+        <v>116800</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
@@ -3049,13 +3049,13 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-16500</v>
+        <v>-16300</v>
       </c>
       <c r="E81" s="3">
-        <v>-8600</v>
+        <v>-8500</v>
       </c>
       <c r="F81" s="3">
-        <v>-35500</v>
+        <v>-35200</v>
       </c>
       <c r="G81" s="3">
         <v>6900</v>
@@ -3064,7 +3064,7 @@
         <v>1800</v>
       </c>
       <c r="I81" s="3">
-        <v>6000</v>
+        <v>5900</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
@@ -3101,22 +3101,22 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>12700</v>
+        <v>12600</v>
       </c>
       <c r="E83" s="3">
-        <v>9900</v>
+        <v>9800</v>
       </c>
       <c r="F83" s="3">
-        <v>9000</v>
+        <v>8900</v>
       </c>
       <c r="G83" s="3">
-        <v>8600</v>
+        <v>8500</v>
       </c>
       <c r="H83" s="3">
-        <v>8400</v>
+        <v>8300</v>
       </c>
       <c r="I83" s="3">
-        <v>7400</v>
+        <v>7300</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -3317,16 +3317,16 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-59900</v>
+        <v>-59500</v>
       </c>
       <c r="E89" s="3">
-        <v>59600</v>
+        <v>59200</v>
       </c>
       <c r="F89" s="3">
-        <v>-18100</v>
+        <v>-18000</v>
       </c>
       <c r="G89" s="3">
-        <v>11500</v>
+        <v>11400</v>
       </c>
       <c r="H89" s="3">
         <v>2600</v>
@@ -3369,10 +3369,10 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-24800</v>
+        <v>-24600</v>
       </c>
       <c r="E91" s="3">
-        <v>-13000</v>
+        <v>-12900</v>
       </c>
       <c r="F91" s="3">
         <v>-3200</v>
@@ -3384,7 +3384,7 @@
         <v>-2000</v>
       </c>
       <c r="I91" s="3">
-        <v>-6000</v>
+        <v>-5900</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
@@ -3477,10 +3477,10 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-24800</v>
+        <v>-24600</v>
       </c>
       <c r="E94" s="3">
-        <v>-13000</v>
+        <v>-12900</v>
       </c>
       <c r="F94" s="3">
         <v>-3100</v>
@@ -3676,13 +3676,13 @@
         <v>-5900</v>
       </c>
       <c r="E100" s="3">
-        <v>-6600</v>
+        <v>-6500</v>
       </c>
       <c r="F100" s="3">
-        <v>94600</v>
+        <v>93900</v>
       </c>
       <c r="G100" s="3">
-        <v>-1000</v>
+        <v>-900</v>
       </c>
       <c r="H100" s="3">
         <v>-2300</v>
@@ -3745,22 +3745,22 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-90700</v>
+        <v>-90100</v>
       </c>
       <c r="E102" s="3">
-        <v>40000</v>
+        <v>39700</v>
       </c>
       <c r="F102" s="3">
-        <v>73300</v>
+        <v>72800</v>
       </c>
       <c r="G102" s="3">
-        <v>7900</v>
+        <v>7800</v>
       </c>
       <c r="H102" s="3">
         <v>-1700</v>
       </c>
       <c r="I102" s="3">
-        <v>-16000</v>
+        <v>-15900</v>
       </c>
       <c r="J102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/MYTE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MYTE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>MYTE</t>
   </si>
@@ -656,52 +656,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44742</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44377</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44012</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43646</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43281</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
@@ -711,32 +711,35 @@
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>830600</v>
+        <v>931300</v>
       </c>
       <c r="E8" s="3">
-        <v>745400</v>
+        <v>848400</v>
       </c>
       <c r="F8" s="3">
-        <v>661500</v>
+        <v>764000</v>
       </c>
       <c r="G8" s="3">
-        <v>485800</v>
+        <v>678000</v>
       </c>
       <c r="H8" s="3">
-        <v>409700</v>
+        <v>497900</v>
       </c>
       <c r="I8" s="3">
-        <v>328000</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+        <v>419900</v>
+      </c>
+      <c r="J8" s="3">
+        <v>336200</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -747,32 +750,35 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>417200</v>
+        <v>498000</v>
       </c>
       <c r="E9" s="3">
-        <v>361800</v>
+        <v>851900</v>
       </c>
       <c r="F9" s="3">
-        <v>351300</v>
+        <v>370800</v>
       </c>
       <c r="G9" s="3">
-        <v>258900</v>
+        <v>360000</v>
       </c>
       <c r="H9" s="3">
-        <v>217700</v>
+        <v>265300</v>
       </c>
       <c r="I9" s="3">
-        <v>173400</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+        <v>223100</v>
+      </c>
+      <c r="J9" s="3">
+        <v>177700</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -783,32 +789,35 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>413500</v>
+        <v>433300</v>
       </c>
       <c r="E10" s="3">
-        <v>383600</v>
+        <v>-3500</v>
       </c>
       <c r="F10" s="3">
-        <v>310200</v>
+        <v>393200</v>
       </c>
       <c r="G10" s="3">
-        <v>226900</v>
+        <v>317900</v>
       </c>
       <c r="H10" s="3">
-        <v>192000</v>
+        <v>232500</v>
       </c>
       <c r="I10" s="3">
-        <v>154600</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>196800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>158400</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -819,9 +828,12 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,8 +848,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -871,9 +884,12 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,23 +923,26 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1000</v>
+        <v>21700</v>
       </c>
       <c r="E14" s="3">
-        <v>4700</v>
+        <v>10300</v>
       </c>
       <c r="F14" s="3">
-        <v>7500</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+        <v>4800</v>
+      </c>
+      <c r="G14" s="3">
+        <v>7700</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -940,35 +959,38 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>12600</v>
+        <v>16800</v>
       </c>
       <c r="E15" s="3">
-        <v>9800</v>
+        <v>25800</v>
       </c>
       <c r="F15" s="3">
-        <v>8900</v>
+        <v>10100</v>
       </c>
       <c r="G15" s="3">
+        <v>9100</v>
+      </c>
+      <c r="H15" s="3">
+        <v>8700</v>
+      </c>
+      <c r="I15" s="3">
         <v>8500</v>
       </c>
-      <c r="H15" s="3">
-        <v>8300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>7300</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+      <c r="J15" s="3">
+        <v>7500</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -979,9 +1001,12 @@
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -993,31 +1018,32 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>837200</v>
+        <v>955600</v>
       </c>
       <c r="E17" s="3">
-        <v>740200</v>
+        <v>858000</v>
       </c>
       <c r="F17" s="3">
-        <v>696200</v>
+        <v>758600</v>
       </c>
       <c r="G17" s="3">
-        <v>463200</v>
+        <v>713600</v>
       </c>
       <c r="H17" s="3">
-        <v>389100</v>
+        <v>474700</v>
       </c>
       <c r="I17" s="3">
-        <v>313100</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>398700</v>
+      </c>
+      <c r="J17" s="3">
+        <v>320900</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1028,32 +1054,35 @@
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-6600</v>
+        <v>-24300</v>
       </c>
       <c r="E18" s="3">
-        <v>5200</v>
+        <v>-9600</v>
       </c>
       <c r="F18" s="3">
-        <v>-34800</v>
+        <v>5400</v>
       </c>
       <c r="G18" s="3">
-        <v>22600</v>
+        <v>-35600</v>
       </c>
       <c r="H18" s="3">
-        <v>20600</v>
+        <v>23200</v>
       </c>
       <c r="I18" s="3">
-        <v>14900</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>21100</v>
+      </c>
+      <c r="J18" s="3">
+        <v>15300</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1064,9 +1093,12 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1081,31 +1113,32 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
-        <v>24200</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>-2300</v>
+        <v>24800</v>
       </c>
       <c r="H20" s="3">
-        <v>-5100</v>
+        <v>-2400</v>
       </c>
       <c r="I20" s="3">
-        <v>4100</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>-5200</v>
+      </c>
+      <c r="J20" s="3">
+        <v>4200</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1116,32 +1149,35 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>6300</v>
+        <v>-7500</v>
       </c>
       <c r="E21" s="3">
-        <v>15000</v>
+        <v>3700</v>
       </c>
       <c r="F21" s="3">
+        <v>15400</v>
+      </c>
+      <c r="G21" s="3">
         <v>-1700</v>
       </c>
-      <c r="G21" s="3">
-        <v>28700</v>
-      </c>
       <c r="H21" s="3">
-        <v>23800</v>
+        <v>29500</v>
       </c>
       <c r="I21" s="3">
-        <v>26300</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>24500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>27100</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1152,32 +1188,35 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>3000</v>
+        <v>5300</v>
       </c>
       <c r="E22" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F22" s="3">
         <v>1100</v>
       </c>
-      <c r="F22" s="3">
-        <v>7900</v>
-      </c>
       <c r="G22" s="3">
-        <v>9700</v>
+        <v>8100</v>
       </c>
       <c r="H22" s="3">
-        <v>10100</v>
+        <v>9900</v>
       </c>
       <c r="I22" s="3">
-        <v>9400</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+        <v>10300</v>
+      </c>
+      <c r="J22" s="3">
+        <v>9600</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1188,32 +1227,35 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-9200</v>
+        <v>-29600</v>
       </c>
       <c r="E23" s="3">
-        <v>4100</v>
+        <v>-12300</v>
       </c>
       <c r="F23" s="3">
-        <v>-18400</v>
+        <v>4200</v>
       </c>
       <c r="G23" s="3">
-        <v>10600</v>
+        <v>-18900</v>
       </c>
       <c r="H23" s="3">
-        <v>5500</v>
+        <v>10800</v>
       </c>
       <c r="I23" s="3">
-        <v>9700</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+        <v>5600</v>
+      </c>
+      <c r="J23" s="3">
+        <v>9900</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1224,32 +1266,35 @@
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>7100</v>
+        <v>-2000</v>
       </c>
       <c r="E24" s="3">
-        <v>12700</v>
+        <v>6500</v>
       </c>
       <c r="F24" s="3">
-        <v>16800</v>
+        <v>13000</v>
       </c>
       <c r="G24" s="3">
-        <v>3700</v>
+        <v>17200</v>
       </c>
       <c r="H24" s="3">
-        <v>3700</v>
+        <v>3800</v>
       </c>
       <c r="I24" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+        <v>3800</v>
+      </c>
+      <c r="J24" s="3">
+        <v>3800</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1260,9 +1305,12 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1296,32 +1344,35 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-16300</v>
+        <v>-27600</v>
       </c>
       <c r="E26" s="3">
-        <v>-8500</v>
+        <v>-18900</v>
       </c>
       <c r="F26" s="3">
-        <v>-35200</v>
+        <v>-8700</v>
       </c>
       <c r="G26" s="3">
-        <v>6900</v>
+        <v>-36100</v>
       </c>
       <c r="H26" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I26" s="3">
         <v>1800</v>
       </c>
-      <c r="I26" s="3">
-        <v>5900</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+      <c r="J26" s="3">
+        <v>6100</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1332,32 +1383,35 @@
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-16300</v>
+        <v>-27600</v>
       </c>
       <c r="E27" s="3">
-        <v>-8500</v>
+        <v>-18900</v>
       </c>
       <c r="F27" s="3">
-        <v>-35200</v>
+        <v>-8700</v>
       </c>
       <c r="G27" s="3">
-        <v>6900</v>
+        <v>-36100</v>
       </c>
       <c r="H27" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I27" s="3">
         <v>1800</v>
       </c>
-      <c r="I27" s="3">
-        <v>5900</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+      <c r="J27" s="3">
+        <v>6100</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1368,9 +1422,12 @@
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1404,9 +1461,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1440,9 +1500,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1476,9 +1539,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1512,32 +1578,35 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
-        <v>-24200</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>2300</v>
+        <v>-24800</v>
       </c>
       <c r="H32" s="3">
-        <v>5100</v>
+        <v>2400</v>
       </c>
       <c r="I32" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>5200</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-4200</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1548,32 +1617,35 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-16300</v>
+        <v>-27600</v>
       </c>
       <c r="E33" s="3">
-        <v>-8500</v>
+        <v>-18900</v>
       </c>
       <c r="F33" s="3">
-        <v>-35200</v>
+        <v>-8700</v>
       </c>
       <c r="G33" s="3">
-        <v>6900</v>
+        <v>-36100</v>
       </c>
       <c r="H33" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I33" s="3">
         <v>1800</v>
       </c>
-      <c r="I33" s="3">
-        <v>5900</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+      <c r="J33" s="3">
+        <v>6100</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1584,9 +1656,12 @@
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1620,32 +1695,35 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-16300</v>
+        <v>-27600</v>
       </c>
       <c r="E35" s="3">
-        <v>-8500</v>
+        <v>-18900</v>
       </c>
       <c r="F35" s="3">
-        <v>-35200</v>
+        <v>-8700</v>
       </c>
       <c r="G35" s="3">
-        <v>6900</v>
+        <v>-36100</v>
       </c>
       <c r="H35" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I35" s="3">
         <v>1800</v>
       </c>
-      <c r="I35" s="3">
-        <v>5900</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+      <c r="J35" s="3">
+        <v>6100</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1656,38 +1734,41 @@
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44742</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44377</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44012</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43646</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43281</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1697,9 +1778,12 @@
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1714,8 +1798,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1730,31 +1815,32 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>32600</v>
+        <v>16700</v>
       </c>
       <c r="E41" s="3">
-        <v>122700</v>
+        <v>33400</v>
       </c>
       <c r="F41" s="3">
-        <v>83000</v>
+        <v>125700</v>
       </c>
       <c r="G41" s="3">
-        <v>10100</v>
+        <v>85000</v>
       </c>
       <c r="H41" s="3">
+        <v>10400</v>
+      </c>
+      <c r="I41" s="3">
         <v>2300</v>
       </c>
-      <c r="I41" s="3">
-        <v>4000</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+      <c r="J41" s="3">
+        <v>4100</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1765,9 +1851,12 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1801,32 +1890,35 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>8100</v>
+        <v>14300</v>
       </c>
       <c r="E43" s="3">
-        <v>8900</v>
+        <v>8300</v>
       </c>
       <c r="F43" s="3">
-        <v>5400</v>
+        <v>9200</v>
       </c>
       <c r="G43" s="3">
-        <v>5200</v>
+        <v>5600</v>
       </c>
       <c r="H43" s="3">
-        <v>6100</v>
+        <v>5300</v>
       </c>
       <c r="I43" s="3">
-        <v>6000</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>6300</v>
+      </c>
+      <c r="J43" s="3">
+        <v>6200</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1837,32 +1929,35 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>389300</v>
+        <v>410500</v>
       </c>
       <c r="E44" s="3">
-        <v>248700</v>
+        <v>399000</v>
       </c>
       <c r="F44" s="3">
-        <v>267000</v>
+        <v>254900</v>
       </c>
       <c r="G44" s="3">
-        <v>182800</v>
+        <v>273600</v>
       </c>
       <c r="H44" s="3">
-        <v>147000</v>
+        <v>187300</v>
       </c>
       <c r="I44" s="3">
-        <v>115300</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+        <v>150700</v>
+      </c>
+      <c r="J44" s="3">
+        <v>118200</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -1873,32 +1968,35 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>45500</v>
+        <v>49000</v>
       </c>
       <c r="E45" s="3">
-        <v>66900</v>
+        <v>46600</v>
       </c>
       <c r="F45" s="3">
-        <v>15800</v>
+        <v>68500</v>
       </c>
       <c r="G45" s="3">
-        <v>20500</v>
+        <v>16200</v>
       </c>
       <c r="H45" s="3">
-        <v>9100</v>
+        <v>21000</v>
       </c>
       <c r="I45" s="3">
-        <v>9800</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+        <v>9300</v>
+      </c>
+      <c r="J45" s="3">
+        <v>10000</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -1909,32 +2007,35 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>475500</v>
+        <v>490500</v>
       </c>
       <c r="E46" s="3">
-        <v>447200</v>
+        <v>487400</v>
       </c>
       <c r="F46" s="3">
-        <v>371200</v>
+        <v>458300</v>
       </c>
       <c r="G46" s="3">
-        <v>218600</v>
+        <v>380500</v>
       </c>
       <c r="H46" s="3">
-        <v>164500</v>
+        <v>224000</v>
       </c>
       <c r="I46" s="3">
-        <v>135100</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+        <v>168600</v>
+      </c>
+      <c r="J46" s="3">
+        <v>138500</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1945,21 +2046,24 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>7100</v>
+        <v>0</v>
       </c>
       <c r="E47" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F47" s="3">
         <v>300</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1975,38 +2079,41 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>99500</v>
+        <v>98700</v>
       </c>
       <c r="E48" s="3">
-        <v>42500</v>
+        <v>101900</v>
       </c>
       <c r="F48" s="3">
-        <v>24700</v>
+        <v>43600</v>
       </c>
       <c r="G48" s="3">
-        <v>30900</v>
+        <v>25300</v>
       </c>
       <c r="H48" s="3">
-        <v>29700</v>
+        <v>31600</v>
       </c>
       <c r="I48" s="3">
-        <v>36100</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+        <v>30500</v>
+      </c>
+      <c r="J48" s="3">
+        <v>37000</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2017,32 +2124,35 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>167800</v>
+        <v>171600</v>
       </c>
       <c r="E49" s="3">
-        <v>167700</v>
+        <v>172000</v>
       </c>
       <c r="F49" s="3">
-        <v>168200</v>
+        <v>171900</v>
       </c>
       <c r="G49" s="3">
-        <v>167500</v>
+        <v>172400</v>
       </c>
       <c r="H49" s="3">
-        <v>167700</v>
+        <v>171600</v>
       </c>
       <c r="I49" s="3">
-        <v>167600</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>171900</v>
+      </c>
+      <c r="J49" s="3">
+        <v>171800</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2053,9 +2163,12 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2089,9 +2202,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2125,33 +2241,36 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E52" s="3">
         <v>100</v>
       </c>
-      <c r="E52" s="3">
-        <v>6600</v>
-      </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>6700</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
       </c>
       <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2161,9 +2280,12 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2197,32 +2319,35 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>750000</v>
+        <v>771500</v>
       </c>
       <c r="E54" s="3">
-        <v>664400</v>
+        <v>768600</v>
       </c>
       <c r="F54" s="3">
-        <v>564100</v>
+        <v>680900</v>
       </c>
       <c r="G54" s="3">
-        <v>416900</v>
+        <v>578100</v>
       </c>
       <c r="H54" s="3">
-        <v>362200</v>
+        <v>427300</v>
       </c>
       <c r="I54" s="3">
-        <v>338900</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>371200</v>
+      </c>
+      <c r="J54" s="3">
+        <v>347300</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2233,9 +2358,12 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2250,8 +2378,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2266,31 +2395,32 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>76800</v>
+        <v>94500</v>
       </c>
       <c r="E57" s="3">
-        <v>48800</v>
+        <v>78700</v>
       </c>
       <c r="F57" s="3">
-        <v>47100</v>
+        <v>50000</v>
       </c>
       <c r="G57" s="3">
-        <v>39100</v>
+        <v>48200</v>
       </c>
       <c r="H57" s="3">
-        <v>31800</v>
+        <v>40000</v>
       </c>
       <c r="I57" s="3">
-        <v>33800</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+        <v>32600</v>
+      </c>
+      <c r="J57" s="3">
+        <v>34600</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2301,32 +2431,35 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>8800</v>
+        <v>10300</v>
       </c>
       <c r="E58" s="3">
-        <v>5600</v>
+        <v>9000</v>
       </c>
       <c r="F58" s="3">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="G58" s="3">
-        <v>17100</v>
+        <v>5900</v>
       </c>
       <c r="H58" s="3">
-        <v>9000</v>
+        <v>17500</v>
       </c>
       <c r="I58" s="3">
-        <v>5400</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>9200</v>
+      </c>
+      <c r="J58" s="3">
+        <v>5500</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2337,32 +2470,35 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>123600</v>
+        <v>136200</v>
       </c>
       <c r="E59" s="3">
-        <v>120500</v>
+        <v>126700</v>
       </c>
       <c r="F59" s="3">
-        <v>81600</v>
+        <v>123500</v>
       </c>
       <c r="G59" s="3">
-        <v>57200</v>
+        <v>83600</v>
       </c>
       <c r="H59" s="3">
-        <v>38800</v>
+        <v>58600</v>
       </c>
       <c r="I59" s="3">
-        <v>26700</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>39700</v>
+      </c>
+      <c r="J59" s="3">
+        <v>27400</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2373,32 +2509,35 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>209300</v>
+        <v>241000</v>
       </c>
       <c r="E60" s="3">
-        <v>174900</v>
+        <v>214500</v>
       </c>
       <c r="F60" s="3">
-        <v>134500</v>
+        <v>179300</v>
       </c>
       <c r="G60" s="3">
-        <v>113300</v>
+        <v>137800</v>
       </c>
       <c r="H60" s="3">
-        <v>79600</v>
+        <v>116100</v>
       </c>
       <c r="I60" s="3">
-        <v>65900</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+        <v>81500</v>
+      </c>
+      <c r="J60" s="3">
+        <v>67600</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2409,32 +2548,35 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>53500</v>
+        <v>44800</v>
       </c>
       <c r="E61" s="3">
-        <v>18200</v>
+        <v>54800</v>
       </c>
       <c r="F61" s="3">
-        <v>9500</v>
+        <v>18600</v>
       </c>
       <c r="G61" s="3">
-        <v>221700</v>
+        <v>9700</v>
       </c>
       <c r="H61" s="3">
-        <v>151000</v>
+        <v>227200</v>
       </c>
       <c r="I61" s="3">
-        <v>143200</v>
+        <v>154800</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>146800</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2445,32 +2587,35 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3600</v>
+        <v>3100</v>
       </c>
       <c r="E62" s="3">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="F62" s="3">
-        <v>3300</v>
+        <v>4900</v>
       </c>
       <c r="G62" s="3">
-        <v>12400</v>
+        <v>3400</v>
       </c>
       <c r="H62" s="3">
-        <v>11300</v>
+        <v>12700</v>
       </c>
       <c r="I62" s="3">
-        <v>12800</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>11600</v>
+      </c>
+      <c r="J62" s="3">
+        <v>13200</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2481,9 +2626,12 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2517,9 +2665,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2553,9 +2704,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2589,32 +2743,35 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>266400</v>
+        <v>288900</v>
       </c>
       <c r="E66" s="3">
-        <v>197900</v>
+        <v>273100</v>
       </c>
       <c r="F66" s="3">
-        <v>147200</v>
+        <v>202800</v>
       </c>
       <c r="G66" s="3">
-        <v>347400</v>
+        <v>150900</v>
       </c>
       <c r="H66" s="3">
-        <v>241900</v>
+        <v>356000</v>
       </c>
       <c r="I66" s="3">
-        <v>222000</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>247900</v>
+      </c>
+      <c r="J66" s="3">
+        <v>227500</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2625,9 +2782,12 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2642,8 +2802,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2677,9 +2838,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2713,9 +2877,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2749,9 +2916,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2785,32 +2955,35 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>481900</v>
+        <v>480900</v>
       </c>
       <c r="E72" s="3">
-        <v>464900</v>
+        <v>493900</v>
       </c>
       <c r="F72" s="3">
-        <v>415100</v>
+        <v>476400</v>
       </c>
       <c r="G72" s="3">
-        <v>67800</v>
+        <v>425400</v>
       </c>
       <c r="H72" s="3">
-        <v>123600</v>
+        <v>69500</v>
       </c>
       <c r="I72" s="3">
-        <v>121700</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>126700</v>
+      </c>
+      <c r="J72" s="3">
+        <v>124700</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2821,9 +2994,12 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2857,9 +3033,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2893,9 +3072,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2929,32 +3111,35 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>483500</v>
+        <v>482500</v>
       </c>
       <c r="E76" s="3">
-        <v>466500</v>
+        <v>495600</v>
       </c>
       <c r="F76" s="3">
-        <v>416800</v>
+        <v>478100</v>
       </c>
       <c r="G76" s="3">
-        <v>69600</v>
+        <v>427200</v>
       </c>
       <c r="H76" s="3">
-        <v>120300</v>
+        <v>71300</v>
       </c>
       <c r="I76" s="3">
-        <v>116800</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>123300</v>
+      </c>
+      <c r="J76" s="3">
+        <v>119700</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2965,9 +3150,12 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3001,38 +3189,41 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44742</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44377</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44012</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43646</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43281</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3042,32 +3233,35 @@
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-16300</v>
+        <v>-27600</v>
       </c>
       <c r="E81" s="3">
-        <v>-8500</v>
+        <v>-18900</v>
       </c>
       <c r="F81" s="3">
-        <v>-35200</v>
+        <v>-8700</v>
       </c>
       <c r="G81" s="3">
-        <v>6900</v>
+        <v>-36100</v>
       </c>
       <c r="H81" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I81" s="3">
         <v>1800</v>
       </c>
-      <c r="I81" s="3">
-        <v>5900</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+      <c r="J81" s="3">
+        <v>6100</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -3078,9 +3272,12 @@
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3095,31 +3292,32 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>12600</v>
+        <v>16800</v>
       </c>
       <c r="E83" s="3">
-        <v>9800</v>
+        <v>12900</v>
       </c>
       <c r="F83" s="3">
-        <v>8900</v>
+        <v>10100</v>
       </c>
       <c r="G83" s="3">
+        <v>9100</v>
+      </c>
+      <c r="H83" s="3">
+        <v>8700</v>
+      </c>
+      <c r="I83" s="3">
         <v>8500</v>
       </c>
-      <c r="H83" s="3">
-        <v>8300</v>
-      </c>
-      <c r="I83" s="3">
-        <v>7300</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+      <c r="J83" s="3">
+        <v>7500</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3130,9 +3328,12 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3166,9 +3367,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3202,9 +3406,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3238,9 +3445,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3274,9 +3484,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3310,32 +3523,35 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-59500</v>
+        <v>11100</v>
       </c>
       <c r="E89" s="3">
-        <v>59200</v>
+        <v>-61000</v>
       </c>
       <c r="F89" s="3">
-        <v>-18000</v>
+        <v>60700</v>
       </c>
       <c r="G89" s="3">
-        <v>11400</v>
+        <v>-18400</v>
       </c>
       <c r="H89" s="3">
+        <v>11700</v>
+      </c>
+      <c r="I89" s="3">
         <v>2600</v>
       </c>
-      <c r="I89" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+      <c r="J89" s="3">
+        <v>-5400</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3346,9 +3562,12 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3363,31 +3582,32 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-24600</v>
+        <v>-13100</v>
       </c>
       <c r="E91" s="3">
-        <v>-12900</v>
+        <v>-25200</v>
       </c>
       <c r="F91" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="G91" s="3">
         <v>-3200</v>
       </c>
-      <c r="G91" s="3">
-        <v>-2600</v>
-      </c>
       <c r="H91" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I91" s="3">
         <v>-2000</v>
       </c>
-      <c r="I91" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+      <c r="J91" s="3">
+        <v>-6100</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3398,9 +3618,12 @@
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3434,9 +3657,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3470,32 +3696,35 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-24600</v>
+        <v>-13100</v>
       </c>
       <c r="E94" s="3">
-        <v>-12900</v>
+        <v>-25200</v>
       </c>
       <c r="F94" s="3">
-        <v>-3100</v>
+        <v>-13200</v>
       </c>
       <c r="G94" s="3">
-        <v>-2600</v>
+        <v>-3200</v>
       </c>
       <c r="H94" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I94" s="3">
         <v>-2000</v>
       </c>
-      <c r="I94" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+      <c r="J94" s="3">
+        <v>-6000</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3506,9 +3735,12 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3523,8 +3755,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3558,9 +3791,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3594,9 +3830,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3630,9 +3869,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3666,32 +3908,35 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-5900</v>
+        <v>-14700</v>
       </c>
       <c r="E100" s="3">
-        <v>-6500</v>
+        <v>-6000</v>
       </c>
       <c r="F100" s="3">
-        <v>93900</v>
+        <v>-6700</v>
       </c>
       <c r="G100" s="3">
-        <v>-900</v>
+        <v>96300</v>
       </c>
       <c r="H100" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-2300</v>
       </c>
-      <c r="I100" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+      <c r="J100" s="3">
+        <v>-4900</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3702,20 +3947,23 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E101" s="3">
         <v>-100</v>
       </c>
       <c r="F101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G101" s="3">
         <v>0</v>
@@ -3726,8 +3974,8 @@
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -3738,32 +3986,35 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-90100</v>
+        <v>-16600</v>
       </c>
       <c r="E102" s="3">
-        <v>39700</v>
+        <v>-92300</v>
       </c>
       <c r="F102" s="3">
-        <v>72800</v>
+        <v>40700</v>
       </c>
       <c r="G102" s="3">
-        <v>7800</v>
+        <v>74600</v>
       </c>
       <c r="H102" s="3">
+        <v>8000</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1700</v>
       </c>
-      <c r="I102" s="3">
-        <v>-15900</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+      <c r="J102" s="3">
+        <v>-16300</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
@@ -3774,7 +4025,10 @@
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/MYTE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MYTE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
   <si>
     <t>MYTE</t>
   </si>
@@ -721,25 +721,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>931300</v>
+        <v>900900</v>
       </c>
       <c r="E8" s="3">
-        <v>848400</v>
+        <v>836200</v>
       </c>
       <c r="F8" s="3">
-        <v>764000</v>
+        <v>719000</v>
       </c>
       <c r="G8" s="3">
-        <v>678000</v>
+        <v>725700</v>
       </c>
       <c r="H8" s="3">
-        <v>497900</v>
+        <v>505800</v>
       </c>
       <c r="I8" s="3">
-        <v>419900</v>
+        <v>431400</v>
       </c>
       <c r="J8" s="3">
-        <v>336200</v>
+        <v>354100</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -760,25 +760,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>498000</v>
+        <v>488900</v>
       </c>
       <c r="E9" s="3">
-        <v>851900</v>
+        <v>421400</v>
       </c>
       <c r="F9" s="3">
-        <v>370800</v>
+        <v>349900</v>
       </c>
       <c r="G9" s="3">
-        <v>360000</v>
+        <v>385400</v>
       </c>
       <c r="H9" s="3">
-        <v>265300</v>
+        <v>269600</v>
       </c>
       <c r="I9" s="3">
-        <v>223100</v>
+        <v>229200</v>
       </c>
       <c r="J9" s="3">
-        <v>177700</v>
+        <v>187200</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -799,25 +799,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>433300</v>
+        <v>412000</v>
       </c>
       <c r="E10" s="3">
-        <v>-3500</v>
+        <v>414800</v>
       </c>
       <c r="F10" s="3">
-        <v>393200</v>
+        <v>369000</v>
       </c>
       <c r="G10" s="3">
-        <v>317900</v>
+        <v>340300</v>
       </c>
       <c r="H10" s="3">
-        <v>232500</v>
+        <v>236300</v>
       </c>
       <c r="I10" s="3">
-        <v>196800</v>
+        <v>202200</v>
       </c>
       <c r="J10" s="3">
-        <v>158400</v>
+        <v>166900</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -933,22 +933,22 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>21700</v>
+        <v>15100</v>
       </c>
       <c r="E14" s="3">
-        <v>10300</v>
+        <v>5900</v>
       </c>
       <c r="F14" s="3">
-        <v>4800</v>
+        <v>2600</v>
       </c>
       <c r="G14" s="3">
-        <v>7700</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+        <v>-700</v>
+      </c>
+      <c r="H14" s="3">
+        <v>5900</v>
+      </c>
+      <c r="I14" s="3">
+        <v>2300</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
@@ -972,25 +972,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>16800</v>
+        <v>16300</v>
       </c>
       <c r="E15" s="3">
-        <v>25800</v>
+        <v>12700</v>
       </c>
       <c r="F15" s="3">
-        <v>10100</v>
+        <v>9500</v>
       </c>
       <c r="G15" s="3">
-        <v>9100</v>
+        <v>9800</v>
       </c>
       <c r="H15" s="3">
+        <v>8900</v>
+      </c>
+      <c r="I15" s="3">
         <v>8700</v>
       </c>
-      <c r="I15" s="3">
-        <v>8500</v>
-      </c>
       <c r="J15" s="3">
-        <v>7500</v>
+        <v>7900</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -1025,25 +1025,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>955600</v>
+        <v>910800</v>
       </c>
       <c r="E17" s="3">
-        <v>858000</v>
+        <v>837500</v>
       </c>
       <c r="F17" s="3">
-        <v>758600</v>
+        <v>715200</v>
       </c>
       <c r="G17" s="3">
-        <v>713600</v>
+        <v>755000</v>
       </c>
       <c r="H17" s="3">
-        <v>474700</v>
+        <v>476500</v>
       </c>
       <c r="I17" s="3">
-        <v>398700</v>
+        <v>406500</v>
       </c>
       <c r="J17" s="3">
-        <v>320900</v>
+        <v>338300</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1064,25 +1064,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-24300</v>
+        <v>-9900</v>
       </c>
       <c r="E18" s="3">
-        <v>-9600</v>
+        <v>-1300</v>
       </c>
       <c r="F18" s="3">
-        <v>5400</v>
+        <v>3700</v>
       </c>
       <c r="G18" s="3">
-        <v>-35600</v>
+        <v>-29200</v>
       </c>
       <c r="H18" s="3">
-        <v>23200</v>
+        <v>29300</v>
       </c>
       <c r="I18" s="3">
-        <v>21100</v>
+        <v>24900</v>
       </c>
       <c r="J18" s="3">
-        <v>15300</v>
+        <v>15800</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1120,25 +1120,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="E20" s="3">
-        <v>400</v>
+        <v>2200</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>-1900</v>
       </c>
       <c r="G20" s="3">
-        <v>24800</v>
+        <v>-16700</v>
       </c>
       <c r="H20" s="3">
-        <v>-2400</v>
+        <v>2400</v>
       </c>
       <c r="I20" s="3">
-        <v>-5200</v>
+        <v>6100</v>
       </c>
       <c r="J20" s="3">
-        <v>4200</v>
+        <v>-4700</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1159,25 +1159,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-7500</v>
+        <v>7900</v>
       </c>
       <c r="E21" s="3">
-        <v>3700</v>
+        <v>9200</v>
       </c>
       <c r="F21" s="3">
-        <v>15400</v>
+        <v>15100</v>
       </c>
       <c r="G21" s="3">
-        <v>-1700</v>
+        <v>-2800</v>
       </c>
       <c r="H21" s="3">
-        <v>29500</v>
+        <v>35800</v>
       </c>
       <c r="I21" s="3">
-        <v>24500</v>
+        <v>27500</v>
       </c>
       <c r="J21" s="3">
-        <v>27100</v>
+        <v>28500</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1198,25 +1198,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>5300</v>
+        <v>5100</v>
       </c>
       <c r="E22" s="3">
         <v>3100</v>
       </c>
       <c r="F22" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="G22" s="3">
-        <v>8100</v>
+        <v>8700</v>
       </c>
       <c r="H22" s="3">
-        <v>9900</v>
+        <v>10100</v>
       </c>
       <c r="I22" s="3">
-        <v>10300</v>
+        <v>10600</v>
       </c>
       <c r="J22" s="3">
-        <v>9600</v>
+        <v>10100</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1237,25 +1237,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-29600</v>
+        <v>-28600</v>
       </c>
       <c r="E23" s="3">
-        <v>-12300</v>
+        <v>-12200</v>
       </c>
       <c r="F23" s="3">
-        <v>4200</v>
+        <v>2000</v>
       </c>
       <c r="G23" s="3">
-        <v>-18900</v>
+        <v>-20200</v>
       </c>
       <c r="H23" s="3">
-        <v>10800</v>
+        <v>11000</v>
       </c>
       <c r="I23" s="3">
-        <v>5600</v>
+        <v>5800</v>
       </c>
       <c r="J23" s="3">
-        <v>9900</v>
+        <v>10500</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1276,25 +1276,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-2000</v>
+        <v>-1900</v>
       </c>
       <c r="E24" s="3">
-        <v>6500</v>
+        <v>6400</v>
       </c>
       <c r="F24" s="3">
-        <v>13000</v>
+        <v>11700</v>
       </c>
       <c r="G24" s="3">
-        <v>17200</v>
+        <v>18400</v>
       </c>
       <c r="H24" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="I24" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="J24" s="3">
-        <v>3800</v>
+        <v>4000</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1354,25 +1354,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-27600</v>
+        <v>-26700</v>
       </c>
       <c r="E26" s="3">
-        <v>-18900</v>
+        <v>-18600</v>
       </c>
       <c r="F26" s="3">
-        <v>-8700</v>
+        <v>-9700</v>
       </c>
       <c r="G26" s="3">
-        <v>-36100</v>
+        <v>-38700</v>
       </c>
       <c r="H26" s="3">
-        <v>7000</v>
+        <v>7100</v>
       </c>
       <c r="I26" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="J26" s="3">
-        <v>6100</v>
+        <v>6400</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1393,25 +1393,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-27600</v>
+        <v>-26700</v>
       </c>
       <c r="E27" s="3">
-        <v>-18900</v>
+        <v>-18600</v>
       </c>
       <c r="F27" s="3">
-        <v>-8700</v>
+        <v>-9700</v>
       </c>
       <c r="G27" s="3">
-        <v>-36100</v>
+        <v>-38700</v>
       </c>
       <c r="H27" s="3">
-        <v>7000</v>
+        <v>7200</v>
       </c>
       <c r="I27" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="J27" s="3">
-        <v>6100</v>
+        <v>6400</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1588,25 +1588,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="E32" s="3">
-        <v>-400</v>
+        <v>-2200</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="G32" s="3">
-        <v>-24800</v>
+        <v>16700</v>
       </c>
       <c r="H32" s="3">
-        <v>2400</v>
+        <v>-2400</v>
       </c>
       <c r="I32" s="3">
-        <v>5200</v>
+        <v>-6100</v>
       </c>
       <c r="J32" s="3">
-        <v>-4200</v>
+        <v>4700</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1627,25 +1627,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-27600</v>
+        <v>-26700</v>
       </c>
       <c r="E33" s="3">
-        <v>-18900</v>
+        <v>-18600</v>
       </c>
       <c r="F33" s="3">
-        <v>-8700</v>
+        <v>-9700</v>
       </c>
       <c r="G33" s="3">
-        <v>-36100</v>
+        <v>-38700</v>
       </c>
       <c r="H33" s="3">
-        <v>7000</v>
+        <v>7100</v>
       </c>
       <c r="I33" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="J33" s="3">
-        <v>6100</v>
+        <v>6400</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1705,25 +1705,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-27600</v>
+        <v>-26700</v>
       </c>
       <c r="E35" s="3">
-        <v>-18900</v>
+        <v>-18600</v>
       </c>
       <c r="F35" s="3">
-        <v>-8700</v>
+        <v>-9700</v>
       </c>
       <c r="G35" s="3">
-        <v>-36100</v>
+        <v>-38700</v>
       </c>
       <c r="H35" s="3">
-        <v>7000</v>
+        <v>7100</v>
       </c>
       <c r="I35" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="J35" s="3">
-        <v>6100</v>
+        <v>6400</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1822,25 +1822,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>16700</v>
+        <v>16200</v>
       </c>
       <c r="E41" s="3">
-        <v>33400</v>
+        <v>32900</v>
       </c>
       <c r="F41" s="3">
-        <v>125700</v>
+        <v>118700</v>
       </c>
       <c r="G41" s="3">
-        <v>85000</v>
+        <v>91000</v>
       </c>
       <c r="H41" s="3">
-        <v>10400</v>
+        <v>10500</v>
       </c>
       <c r="I41" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="J41" s="3">
-        <v>4100</v>
+        <v>4300</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1867,16 +1867,16 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -1900,25 +1900,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>14300</v>
+        <v>13800</v>
       </c>
       <c r="E43" s="3">
-        <v>8300</v>
+        <v>10500</v>
       </c>
       <c r="F43" s="3">
-        <v>9200</v>
+        <v>44200</v>
       </c>
       <c r="G43" s="3">
-        <v>5600</v>
+        <v>7000</v>
       </c>
       <c r="H43" s="3">
-        <v>5300</v>
+        <v>10800</v>
       </c>
       <c r="I43" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="J43" s="3">
-        <v>6200</v>
+        <v>6500</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1939,25 +1939,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>410500</v>
+        <v>397100</v>
       </c>
       <c r="E44" s="3">
-        <v>399000</v>
+        <v>393300</v>
       </c>
       <c r="F44" s="3">
-        <v>254900</v>
+        <v>240600</v>
       </c>
       <c r="G44" s="3">
-        <v>273600</v>
+        <v>292900</v>
       </c>
       <c r="H44" s="3">
-        <v>187300</v>
+        <v>190300</v>
       </c>
       <c r="I44" s="3">
-        <v>150700</v>
+        <v>154800</v>
       </c>
       <c r="J44" s="3">
-        <v>118200</v>
+        <v>124500</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -1978,25 +1978,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>49000</v>
+        <v>42800</v>
       </c>
       <c r="E45" s="3">
-        <v>46600</v>
+        <v>39500</v>
       </c>
       <c r="F45" s="3">
-        <v>68500</v>
+        <v>22900</v>
       </c>
       <c r="G45" s="3">
-        <v>16200</v>
+        <v>9900</v>
       </c>
       <c r="H45" s="3">
-        <v>21000</v>
+        <v>11600</v>
       </c>
       <c r="I45" s="3">
-        <v>9300</v>
+        <v>6800</v>
       </c>
       <c r="J45" s="3">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2017,25 +2017,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>490500</v>
+        <v>474500</v>
       </c>
       <c r="E46" s="3">
-        <v>487400</v>
+        <v>480400</v>
       </c>
       <c r="F46" s="3">
-        <v>458300</v>
+        <v>432600</v>
       </c>
       <c r="G46" s="3">
-        <v>380500</v>
+        <v>407100</v>
       </c>
       <c r="H46" s="3">
-        <v>224000</v>
+        <v>227600</v>
       </c>
       <c r="I46" s="3">
-        <v>168600</v>
+        <v>173200</v>
       </c>
       <c r="J46" s="3">
-        <v>138500</v>
+        <v>145900</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -2055,14 +2055,14 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>7300</v>
-      </c>
-      <c r="F47" s="3">
-        <v>300</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
@@ -2095,25 +2095,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>98700</v>
+        <v>95500</v>
       </c>
       <c r="E48" s="3">
-        <v>101900</v>
+        <v>100500</v>
       </c>
       <c r="F48" s="3">
-        <v>43600</v>
+        <v>41200</v>
       </c>
       <c r="G48" s="3">
-        <v>25300</v>
+        <v>27100</v>
       </c>
       <c r="H48" s="3">
-        <v>31600</v>
+        <v>32200</v>
       </c>
       <c r="I48" s="3">
-        <v>30500</v>
+        <v>31300</v>
       </c>
       <c r="J48" s="3">
-        <v>37000</v>
+        <v>39000</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2134,25 +2134,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>171600</v>
+        <v>166000</v>
       </c>
       <c r="E49" s="3">
-        <v>172000</v>
+        <v>169500</v>
       </c>
       <c r="F49" s="3">
-        <v>171900</v>
+        <v>162300</v>
       </c>
       <c r="G49" s="3">
-        <v>172400</v>
+        <v>184500</v>
       </c>
       <c r="H49" s="3">
-        <v>171600</v>
+        <v>174400</v>
       </c>
       <c r="I49" s="3">
-        <v>171900</v>
+        <v>176600</v>
       </c>
       <c r="J49" s="3">
-        <v>171800</v>
+        <v>180900</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2251,19 +2251,19 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10600</v>
+        <v>8100</v>
       </c>
       <c r="E52" s="3">
-        <v>100</v>
+        <v>7200</v>
       </c>
       <c r="F52" s="3">
-        <v>6700</v>
+        <v>300</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I52" s="3">
         <v>200</v>
@@ -2329,25 +2329,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>771500</v>
+        <v>746300</v>
       </c>
       <c r="E54" s="3">
-        <v>768600</v>
+        <v>757600</v>
       </c>
       <c r="F54" s="3">
-        <v>680900</v>
+        <v>642700</v>
       </c>
       <c r="G54" s="3">
-        <v>578100</v>
+        <v>618900</v>
       </c>
       <c r="H54" s="3">
-        <v>427300</v>
+        <v>434200</v>
       </c>
       <c r="I54" s="3">
-        <v>371200</v>
+        <v>381400</v>
       </c>
       <c r="J54" s="3">
-        <v>347300</v>
+        <v>365800</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2402,25 +2402,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>94500</v>
+        <v>91400</v>
       </c>
       <c r="E57" s="3">
-        <v>78700</v>
+        <v>77600</v>
       </c>
       <c r="F57" s="3">
-        <v>50000</v>
+        <v>47200</v>
       </c>
       <c r="G57" s="3">
-        <v>48200</v>
+        <v>51600</v>
       </c>
       <c r="H57" s="3">
-        <v>40000</v>
+        <v>40700</v>
       </c>
       <c r="I57" s="3">
-        <v>32600</v>
+        <v>33500</v>
       </c>
       <c r="J57" s="3">
-        <v>34600</v>
+        <v>36500</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2441,25 +2441,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>10300</v>
+        <v>9900</v>
       </c>
       <c r="E58" s="3">
-        <v>9000</v>
+        <v>8900</v>
       </c>
       <c r="F58" s="3">
-        <v>5700</v>
+        <v>5400</v>
       </c>
       <c r="G58" s="3">
-        <v>5900</v>
+        <v>6400</v>
       </c>
       <c r="H58" s="3">
-        <v>17500</v>
+        <v>17800</v>
       </c>
       <c r="I58" s="3">
-        <v>9200</v>
+        <v>9500</v>
       </c>
       <c r="J58" s="3">
-        <v>5500</v>
+        <v>5800</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2480,25 +2480,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>136200</v>
+        <v>67200</v>
       </c>
       <c r="E59" s="3">
-        <v>126700</v>
+        <v>87900</v>
       </c>
       <c r="F59" s="3">
-        <v>123500</v>
+        <v>69500</v>
       </c>
       <c r="G59" s="3">
-        <v>83600</v>
+        <v>44300</v>
       </c>
       <c r="H59" s="3">
-        <v>58600</v>
+        <v>21600</v>
       </c>
       <c r="I59" s="3">
-        <v>39700</v>
+        <v>16700</v>
       </c>
       <c r="J59" s="3">
-        <v>27400</v>
+        <v>17000</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2519,25 +2519,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>241000</v>
+        <v>233100</v>
       </c>
       <c r="E60" s="3">
-        <v>214500</v>
+        <v>216200</v>
       </c>
       <c r="F60" s="3">
-        <v>179300</v>
+        <v>169200</v>
       </c>
       <c r="G60" s="3">
-        <v>137800</v>
+        <v>147500</v>
       </c>
       <c r="H60" s="3">
-        <v>116100</v>
+        <v>122300</v>
       </c>
       <c r="I60" s="3">
-        <v>81500</v>
+        <v>83800</v>
       </c>
       <c r="J60" s="3">
-        <v>67600</v>
+        <v>71200</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2558,25 +2558,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>44800</v>
+        <v>43400</v>
       </c>
       <c r="E61" s="3">
-        <v>54800</v>
+        <v>54100</v>
       </c>
       <c r="F61" s="3">
-        <v>18600</v>
+        <v>17600</v>
       </c>
       <c r="G61" s="3">
-        <v>9700</v>
+        <v>10400</v>
       </c>
       <c r="H61" s="3">
-        <v>227200</v>
+        <v>230800</v>
       </c>
       <c r="I61" s="3">
-        <v>154800</v>
+        <v>159000</v>
       </c>
       <c r="J61" s="3">
-        <v>146800</v>
+        <v>154700</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2597,25 +2597,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="E62" s="3">
-        <v>3700</v>
+        <v>2900</v>
       </c>
       <c r="F62" s="3">
-        <v>4900</v>
+        <v>800</v>
       </c>
       <c r="G62" s="3">
-        <v>3400</v>
+        <v>900</v>
       </c>
       <c r="H62" s="3">
-        <v>12700</v>
+        <v>7300</v>
       </c>
       <c r="I62" s="3">
-        <v>11600</v>
+        <v>6000</v>
       </c>
       <c r="J62" s="3">
-        <v>13200</v>
+        <v>7700</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2753,25 +2753,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>288900</v>
+        <v>279500</v>
       </c>
       <c r="E66" s="3">
-        <v>273100</v>
+        <v>273500</v>
       </c>
       <c r="F66" s="3">
-        <v>202800</v>
+        <v>191400</v>
       </c>
       <c r="G66" s="3">
-        <v>150900</v>
+        <v>161500</v>
       </c>
       <c r="H66" s="3">
-        <v>356000</v>
+        <v>361700</v>
       </c>
       <c r="I66" s="3">
-        <v>247900</v>
+        <v>254700</v>
       </c>
       <c r="J66" s="3">
-        <v>227500</v>
+        <v>239700</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2965,25 +2965,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>480900</v>
+        <v>-120800</v>
       </c>
       <c r="E72" s="3">
-        <v>493900</v>
+        <v>-95900</v>
       </c>
       <c r="F72" s="3">
-        <v>476400</v>
+        <v>-71900</v>
       </c>
       <c r="G72" s="3">
-        <v>425400</v>
+        <v>-72100</v>
       </c>
       <c r="H72" s="3">
-        <v>69500</v>
+        <v>-31800</v>
       </c>
       <c r="I72" s="3">
-        <v>126700</v>
+        <v>-39400</v>
       </c>
       <c r="J72" s="3">
-        <v>124700</v>
+        <v>-42300</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -3121,25 +3121,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>482500</v>
+        <v>466800</v>
       </c>
       <c r="E76" s="3">
-        <v>495600</v>
+        <v>484100</v>
       </c>
       <c r="F76" s="3">
-        <v>478100</v>
+        <v>451300</v>
       </c>
       <c r="G76" s="3">
-        <v>427200</v>
+        <v>457300</v>
       </c>
       <c r="H76" s="3">
-        <v>71300</v>
+        <v>72400</v>
       </c>
       <c r="I76" s="3">
-        <v>123300</v>
+        <v>126700</v>
       </c>
       <c r="J76" s="3">
-        <v>119700</v>
+        <v>126100</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -3243,25 +3243,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-27600</v>
+        <v>-26700</v>
       </c>
       <c r="E81" s="3">
-        <v>-18900</v>
+        <v>-18600</v>
       </c>
       <c r="F81" s="3">
-        <v>-8700</v>
+        <v>-9700</v>
       </c>
       <c r="G81" s="3">
-        <v>-36100</v>
+        <v>-38700</v>
       </c>
       <c r="H81" s="3">
-        <v>7000</v>
+        <v>7100</v>
       </c>
       <c r="I81" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="J81" s="3">
-        <v>6100</v>
+        <v>6400</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -3299,25 +3299,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>16800</v>
+        <v>15800</v>
       </c>
       <c r="E83" s="3">
-        <v>12900</v>
+        <v>12100</v>
       </c>
       <c r="F83" s="3">
-        <v>10100</v>
+        <v>9500</v>
       </c>
       <c r="G83" s="3">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="H83" s="3">
+        <v>8400</v>
+      </c>
+      <c r="I83" s="3">
         <v>8700</v>
       </c>
-      <c r="I83" s="3">
-        <v>8500</v>
-      </c>
       <c r="J83" s="3">
-        <v>7500</v>
+        <v>7400</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3533,25 +3533,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>11100</v>
+        <v>10700</v>
       </c>
       <c r="E89" s="3">
-        <v>-61000</v>
+        <v>-60100</v>
       </c>
       <c r="F89" s="3">
-        <v>60700</v>
+        <v>57300</v>
       </c>
       <c r="G89" s="3">
-        <v>-18400</v>
+        <v>-19700</v>
       </c>
       <c r="H89" s="3">
-        <v>11700</v>
+        <v>11900</v>
       </c>
       <c r="I89" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="J89" s="3">
-        <v>-5400</v>
+        <v>-5700</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3589,25 +3589,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-13100</v>
+        <v>-12700</v>
       </c>
       <c r="E91" s="3">
-        <v>-25200</v>
+        <v>-24800</v>
       </c>
       <c r="F91" s="3">
-        <v>-13200</v>
+        <v>-12500</v>
       </c>
       <c r="G91" s="3">
-        <v>-3200</v>
+        <v>-3500</v>
       </c>
       <c r="H91" s="3">
         <v>-2700</v>
       </c>
       <c r="I91" s="3">
-        <v>-2000</v>
+        <v>-2100</v>
       </c>
       <c r="J91" s="3">
-        <v>-6100</v>
+        <v>-2800</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3706,25 +3706,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-13100</v>
+        <v>-12700</v>
       </c>
       <c r="E94" s="3">
-        <v>-25200</v>
+        <v>-24800</v>
       </c>
       <c r="F94" s="3">
-        <v>-13200</v>
+        <v>-12500</v>
       </c>
       <c r="G94" s="3">
-        <v>-3200</v>
+        <v>-3400</v>
       </c>
       <c r="H94" s="3">
         <v>-2700</v>
       </c>
       <c r="I94" s="3">
-        <v>-2000</v>
+        <v>-2100</v>
       </c>
       <c r="J94" s="3">
-        <v>-6000</v>
+        <v>-2800</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3918,25 +3918,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-14700</v>
+        <v>-14200</v>
       </c>
       <c r="E100" s="3">
-        <v>-6000</v>
+        <v>-5900</v>
       </c>
       <c r="F100" s="3">
-        <v>-6700</v>
+        <v>-6300</v>
       </c>
       <c r="G100" s="3">
-        <v>96300</v>
+        <v>103100</v>
       </c>
       <c r="H100" s="3">
         <v>-1000</v>
       </c>
       <c r="I100" s="3">
-        <v>-2300</v>
+        <v>-2400</v>
       </c>
       <c r="J100" s="3">
-        <v>-4900</v>
+        <v>-1000</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3971,11 +3971,11 @@
       <c r="H101" s="3">
         <v>0</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -3996,25 +3996,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-16600</v>
+        <v>-16100</v>
       </c>
       <c r="E102" s="3">
-        <v>-92300</v>
+        <v>-91000</v>
       </c>
       <c r="F102" s="3">
-        <v>40700</v>
+        <v>38400</v>
       </c>
       <c r="G102" s="3">
-        <v>74600</v>
+        <v>79900</v>
       </c>
       <c r="H102" s="3">
-        <v>8000</v>
+        <v>8200</v>
       </c>
       <c r="I102" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="J102" s="3">
-        <v>-16300</v>
+        <v>-9500</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
